--- a/stockflow-crm/docs/test-cases/Casos_de_Prueba_StockFlow.xlsx
+++ b/stockflow-crm/docs/test-cases/Casos_de_Prueba_StockFlow.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G225"/>
+  <dimension ref="A1:G236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Suite de tests: pytest + httpx + pytest-mock  |  Base de datos: SQLite in-memory  |  Total: 211 casos  |  Resultado esperado: 0 fallos</t>
+          <t>Suite de tests: pytest + httpx + pytest-mock  |  Base de datos: SQLite in-memory  |  Total: 222 casos  |  Resultado esperado: 0 fallos</t>
         </is>
       </c>
     </row>
@@ -2018,153 +2018,153 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="45" ht="75" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>CP-040</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Organizaciones y Usuarios</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>El foco no se escapa de una ventana modal</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Ventana de alta abierta, navegando con teclado</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Tab desde el último control y Shift+Tab desde el primero</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>El foco vuelve al otro extremo. Antes saltaba al menú lateral, detrás del velo, y un Enter ahí perdía el formulario a medio cargar</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Seguridad</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="53.3" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>CP-040</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="53.3" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>CP-041</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Hash de contraseña con bcrypt</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>hash_password('secret123')</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>El resultado empieza con '$2b$'. Verificable con verify_password.</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="40.28" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>CP-041</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40.28" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>CP-042</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>Verificación correcta de contraseña hasheada</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>Password hasheado</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>verify_password('secret123', hash)</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>Retorna True.</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="35.94" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>CP-042</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="35.94" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>CP-043</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Verificación incorrecta de contraseña</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Password hasheado</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>verify_password('wrongpass', hash)</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>Retorna False.</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="40.9" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>CP-043</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Creación de token JWT contiene sub y exp</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>create_access_token({'sub': 'test@test.com'})</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>JWT decodificable que contiene 'sub' y 'exp'.</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2186,207 +2186,207 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
+          <t>Creación de token JWT contiene sub y exp</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>create_access_token({'sub': 'test@test.com'})</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>JWT decodificable que contiene 'sub' y 'exp'.</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40.9" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>CP-045</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
           <t>Token JWT no expirado se valida correctamente</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Token válido</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>decode_access_token(token válido)</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>Devuelve payload con sub='test@test.com'.</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="34.7" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>CP-045</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34.7" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>CP-046</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Token JWT expirado lanza JWTError</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>Token con exp en el pasado</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>decode_access_token(token expirado)</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>Lanza jose.JWTError.</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="42.14" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>CP-046</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42.14" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>CP-047</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Token firmado con clave incorrecta es rechazado</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Token firmado con otra clave</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>decode_access_token(token con firma inválida)</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>Lanza jose.JWTError.</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="33.46" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>CP-047</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="33.46" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>CP-048</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>Payload malformado lanza JWTError</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>decode_access_token('not.a.jwt')</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>Lanza jose.JWTError.</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="55.16" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>CP-048</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="55.16" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>CP-049</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>create_access_token acepta timedelta personalizado</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>create_access_token({'sub':'u'}, expires_delta=timedelta(minutes=5))</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>Token creado; exp ≈ now + 5 min.</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="75" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>CP-049</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>El error 500 conserva las cabeceras CORS</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Origen permitido; se fuerza un fallo no controlado</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>GET /products con Origin del frontend y un error interno</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 500 con Access-Control-Allow-Origin: sin esa cabecera el navegador bloquea la respuesta y el cliente reporta falta de conexión en vez del error real</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2408,2263 +2408,2263 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
+          <t>El error 500 conserva las cabeceras CORS</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Origen permitido; se fuerza un fallo no controlado</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>GET /products con Origin del frontend y un error interno</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 500 con Access-Control-Allow-Origin: sin esa cabecera el navegador bloquea la respuesta y el cliente reporta falta de conexión en vez del error real</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="75" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>CP-051</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
           <t>No se refleja un origen no permitido en el error 500</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Origen ajeno a la lista blanca</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>GET /products con Origin de un sitio no autorizado y error interno</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>HTTP 500 sin cabecera Allow-Origin: reflejar cualquier origen abriría un agujero que el resto de la aplicación no tiene</t>
         </is>
       </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="75" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>CP-052</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Una conexión caída se reemplaza sola</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Conexión devuelta al pool después de que el servidor la cerró</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Cualquier consulta posterior</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Responde normalmente. Sin la comprobación previa, la primera acción tras un rato de inactividad fallaba con error 500, incluido el login</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="75" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>CP-053</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Las conexiones se renuevan antes del corte del pooler</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Motor de la aplicación</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Revisión de la configuración del pool</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>El reciclado está por debajo del tiempo de espera del pooler, para no depender solo de que el reintento detecte el corte</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Productos</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="52.06" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>CP-051</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+    <row r="61" ht="52.06" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>CP-054</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>Crear producto exitosamente</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>DB vacía, usuario autenticado</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>POST /products {sku, name, price, current_stock, minimum_stock}</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — devuelve producto con is_active=True.</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="48.34" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>CP-052</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48.34" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>CP-055</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>Crear producto con stock &gt; 0 genera movimiento de entrada</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>POST /products {current_stock:'25.000'}</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>Se crea un StockMovement de tipo 'entry' con quantity=25.</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="43.38" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>CP-053</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="43.38" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>CP-056</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>Crear producto con stock = 0 no genera movimiento</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>POST /products {current_stock:'0.000'}</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>No existe ningún StockMovement para ese producto.</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="40.28" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>CP-054</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40.28" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>CP-057</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>SKU duplicado devuelve 400</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>Producto 'DUP-SKU' ya existe</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>POST /products {sku:'DUP-SKU', ...}</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <t>HTTP 400 — detail contiene 'already exists'.</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="40.9" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>CP-055</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40.9" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>CP-058</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>Crear producto sin autenticación devuelve 401</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>Sin token</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>POST /products sin header Authorization</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>HTTP 401.</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="31.6" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>CP-056</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="31.6" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>CP-059</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>Listar productos — lista vacía</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>Sin productos en DB</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>GET /products</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — devuelve [].</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32.84" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>CP-057</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32.84" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>CP-060</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>Listar productos devuelve todos</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>2 productos en DB</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>GET /products</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — array de 2 elementos.</t>
         </is>
       </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="39.04" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>CP-058</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="39.04" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>CP-061</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>Filtro low_stock_only filtra correctamente</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>Producto Low (stock&lt;min) y OK (stock≥min)</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>GET /products?low_stock_only=true</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <t>Sólo devuelve producto 'Low'.</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="37.18" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>CP-059</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="37.18" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>CP-062</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>Campo low_stock calculado correctamente</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Producto con stock=3 y min=10</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>GET /products</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>low_stock=True en ese producto.</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="29.12" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>CP-060</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="29.12" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>CP-063</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>Obtener producto existente</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>Producto creado</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>GET /products/{id}</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — id coincide.</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="38.42" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>CP-061</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="38.42" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>CP-064</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Obtener producto inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>GET /products/9999</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="44" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>CP-062</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="44" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>CP-065</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>Actualizar nombre y precio</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>Producto existente</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>PUT /products/{id} {name:'Updated', price:'19.99'}</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — name y price actualizados.</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="44.62" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>CP-063</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="44.62" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>CP-066</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>Actualizar stock crea movimiento de ajuste positivo</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Producto con stock=50</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>PUT /products/{id} {current_stock:'60.000'}</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>Movimiento 'adjustment' con quantity=10.</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="44.62" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>CP-064</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="44.62" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>CP-067</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>Actualizar stock crea movimiento de ajuste negativo</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>Producto con stock=50</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>PUT /products/{id} {current_stock:'30.000'}</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>Movimiento 'adjustment' con quantity=-20.</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="40.28" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>CP-065</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="40.28" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>CP-068</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>Actualizar producto inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>PUT /products/9999 {name:'Ghost'}</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="41.52" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>CP-066</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="41.52" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>CP-069</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>Eliminar producto sin movimientos exitosamente</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>Producto sin historial (stock=0)</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>DELETE /products/{id}</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>HTTP 204 — GET posterior devuelve 404.</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="44" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>CP-067</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>CP-070</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>Eliminar producto con movimientos devuelve 409</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>Producto con stock&gt;0 (tiene movimiento de entrada)</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>DELETE /products/{id}</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <t>HTTP 409.</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="39.04" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>CP-068</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="39.04" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>CP-071</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>Eliminar producto inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>DELETE /products/9999</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="48.96" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>CP-069</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="48.96" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>CP-072</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>El nombre de producto admite números</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>POST /products {name:'Tornillo 3/8'}</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — los dígitos son válidos en nombres de producto.</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="40.9" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>CP-070</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="40.9" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>CP-073</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>Nombre vacío devuelve 422 con mensaje legible</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>POST /products {name:''}</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 — 'errors' señala el campo name.</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="35.94" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>CP-071</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="35.94" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>CP-074</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>SKU con espacios devuelve 422</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>POST /products {sku:'AB 123'}</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 — el SKU no admite espacios.</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="31.6" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>CP-072</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="31.6" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>CP-075</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>Precio negativo devuelve 422</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>POST /products {price:'-5.00'}</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <t>HTTP 422.</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="55.16" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>CP-073</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="55.16" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>CP-076</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>Stock decimal rechazado por defecto</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Producto por unidad (allow_decimal_stock=false)</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>POST /products {current_stock:'2.500'}</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 — los artículos por unidad solo admiten cantidades enteras.</t>
         </is>
       </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="52.68" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>CP-074</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="52.68" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>CP-077</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>Stock decimal permitido en artículos a granel</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
         <is>
           <t>allow_decimal_stock=true</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>POST /products {current_stock:'2.500', allow_decimal_stock:true}</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — se aceptan hasta 3 decimales.</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="42.14" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>CP-075</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="42.14" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>CP-078</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>Ajustar a decimal un producto unitario da error</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>Producto por unidad existente</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>PUT /products/{id} {current_stock:'7.250'}</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 con el motivo.</t>
         </is>
       </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="52.06" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>CP-076</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="52.06" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>CP-079</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>No se puede quitar el flag con stock decimal</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D86" s="6" t="inlineStr">
         <is>
           <t>Producto a granel con stock fraccionario</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>PUT /products/{id} {allow_decimal_stock:false}</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 — habría que ajustar antes el stock a un valor entero.</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="51.44" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>CP-077</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="51.44" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>CP-080</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>No se puede borrar un producto con stock pendiente</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>Producto con current_stock &gt; 0</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>DELETE /products/{id}</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>HTTP 409 — indica que primero hay que ajustar el stock a cero.</t>
         </is>
       </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="55.16" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>CP-078</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="55.16" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>CP-081</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>Se puede borrar tras ajustar el stock a cero</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>Producto sin historial comercial</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>PUT /products/{id} {current_stock:'0'} y luego DELETE /products/{id}</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>HTTP 204 — la baja procede una vez que el stock queda en cero.</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="58.26" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>CP-079</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="58.26" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>CP-082</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>Los movimientos internos se borran con el producto</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>Producto con movimientos de ajuste propios</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>DELETE /products/{id}</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>HTTP 204 — los movimientos generados internamente se eliminan en cascada.</t>
         </is>
       </c>
-      <c r="G86" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="41.52" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>CP-080</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="41.52" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>CP-083</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>No se puede borrar con historial de pedidos</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>Producto incluido en un pedido</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>DELETE /products/{id}</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>HTTP 409 — se protege la integridad histórica.</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="51.44" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>CP-081</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="51.44" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>CP-084</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>El mismo SKU puede repetirse en otra organización</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>SKU ya usado en la organización A</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>POST /products {sku: mismo} con token de la organización B</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — la unicidad del SKU es por organización, no global.</t>
         </is>
       </c>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="73.14" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>CP-082</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="73.14" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>CP-085</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>Un precio desmedido da 422 y no error de servidor</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D92" s="6" t="inlineStr">
         <is>
           <t>Sesión válida</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E92" s="6" t="inlineStr">
         <is>
           <t>POST /products con price de 14 dígitos</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 — el límite del esquema replica el de la columna, así que el valor no llega a PostgreSQL</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="51.44" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>CP-083</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="51.44" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>CP-086</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Un stock desmedido da 422</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Sesión válida</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>POST /products con current_stock fuera del rango de la columna</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 con el error señalado en el campo</t>
         </is>
       </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="75" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>CP-084</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="75" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>CP-087</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>El mensaje del límite dice cuál es el límite</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>Sesión válida</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>POST /products con un importe que excede los dígitos admitidos</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <t>El mensaje nombra el tope concreto en lugar de un genérico «el valor no es válido», que deja probando números hasta acertar</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="75" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>CP-088</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Editar un campo no pisa lo que cambió otra persona</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Dos personas con la misma ficha abierta</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Una guarda el precio; la otra, después, guarda el nombre</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Los dos cambios sobreviven. Antes se enviaba el registro completo y el segundo guardado devolvía el precio a su valor viejo, sin aviso</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="75" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>CP-089</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Guardar sin editar nada no envía nada</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Ficha abierta y cerrada con «Guardar» sin tocar campos</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>PUT /products/{id}</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>El cuerpo va vacío: «10.00» y 10 son el mismo valor y no cuentan como cambio, así que no se pisa el trabajo de nadie</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Proveedores</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="44.62" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>CP-085</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
+    <row r="98" ht="44.62" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>CP-090</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>Crear proveedor con todos los campos</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D98" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E98" s="6" t="inlineStr">
         <is>
           <t>POST /suppliers {name, contact_name, email, phone}</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — devuelve todos los campos incluyendo id.</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="47.1" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>CP-086</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="47.1" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>CP-091</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>Crear proveedor sin teléfono (campo opcional)</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>POST /suppliers {name, contact_name, email} (sin phone)</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — phone=null.</t>
         </is>
       </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="52.06" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>CP-087</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="52.06" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>CP-092</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>Crear proveedor sin campos obligatorios devuelve 422</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>POST /suppliers {name:'Incomplete'} (sin contact_name ni email)</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <t>HTTP 422.</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="41.52" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>CP-088</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="41.52" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>CP-093</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>Crear proveedor sin autenticación devuelve 401</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>Sin token</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>POST /suppliers {name:'Anon'}</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <t>HTTP 401.</t>
         </is>
       </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="32.84" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>CP-089</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="32.84" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>CP-094</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>Listar proveedores — lista vacía</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D102" s="6" t="inlineStr">
         <is>
           <t>Sin proveedores</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E102" s="6" t="inlineStr">
         <is>
           <t>GET /suppliers</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — devuelve [].</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="33.46" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>CP-090</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="33.46" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>CP-095</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>Listar proveedores devuelve todos</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>2 proveedores en DB</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>GET /suppliers</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — array de 2 elementos.</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="40.9" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>CP-091</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="40.9" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>CP-096</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>Proveedores se devuelven ordenados por nombre</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D104" s="6" t="inlineStr">
         <is>
           <t>Proveedores 'Zeta' y 'Alpha'</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E104" s="6" t="inlineStr">
         <is>
           <t>GET /suppliers</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <t>El primer elemento es 'Alpha'.</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="29.74" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>CP-092</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="29.74" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>CP-097</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>Obtener proveedor existente</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D105" s="6" t="inlineStr">
         <is>
           <t>Proveedor creado</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>GET /suppliers/{id}</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — id coincide.</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="39.04" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>CP-093</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="39.04" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>CP-098</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>Obtener proveedor inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>GET /suppliers/9999</t>
         </is>
       </c>
-      <c r="F101" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="35.94" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>CP-094</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="35.94" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>CP-099</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>Actualizar nombre del proveedor</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>Proveedor existente</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E107" s="6" t="inlineStr">
         <is>
           <t>PUT /suppliers/{id} {name:'New Name'}</t>
         </is>
       </c>
-      <c r="F102" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — name='New Name'.</t>
         </is>
       </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="40.9" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>CP-095</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="40.9" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>CP-100</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>Actualizar proveedor inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E108" s="6" t="inlineStr">
         <is>
           <t>PUT /suppliers/9999 {name:'Ghost'}</t>
         </is>
       </c>
-      <c r="F103" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="36.56" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>CP-096</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="36.56" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>CP-101</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>Eliminar proveedor exitosamente</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>Proveedor existente</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>DELETE /suppliers/{id}</t>
         </is>
       </c>
-      <c r="F104" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <t>HTTP 204 — GET posterior devuelve 404.</t>
         </is>
       </c>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="39.66" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>CP-097</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="39.66" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>CP-102</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>Eliminar proveedor inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>DELETE /suppliers/9999</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="63.22" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>CP-098</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="63.22" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>CP-103</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>Un proveedor con facturas no se puede eliminar</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>Proveedor con una factura cargada</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>DELETE /suppliers/{id}</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <t>HTTP 409 nombrando las facturas, no el mensaje genérico de integridad referencial</t>
         </is>
       </c>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="52.06" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>CP-099</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="52.06" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>CP-104</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>El listado avisa por adelantado que no se puede borrar</t>
         </is>
       </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="D112" s="6" t="inlineStr">
         <is>
           <t>Un proveedor con facturas</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E112" s="6" t="inlineStr">
         <is>
           <t>GET /suppliers</t>
         </is>
       </c>
-      <c r="F107" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <t>can_delete=false y el motivo, igual que en productos y clientes</t>
         </is>
       </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Facturas (IA)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="55.16" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>CP-100</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
+    <row r="114" ht="55.16" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>CP-105</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>Procesar factura exitosamente (Gemini mockeado)</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>Usuario autenticado. Gemini mock devuelve 2 ítems.</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E114" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process {file: invoice.pdf}</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — devuelve invoice_id, 2 items, supplier='Acme Corp', date.</t>
         </is>
       </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="50.82" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>CP-101</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="50.82" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>CP-106</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>Proceso asocia proveedor si el nombre coincide</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>Proveedor 'Acme Corp' en DB</t>
         </is>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="E115" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process (Gemini devuelve supplier:'Acme Corp')</t>
         </is>
       </c>
-      <c r="F110" s="6" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <t>supplier_id no es null en la respuesta.</t>
         </is>
       </c>
-      <c r="G110" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="56.4" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>CP-102</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="56.4" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>CP-107</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>Proceso sugiere producto existente que coincide</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="D116" s="6" t="inlineStr">
         <is>
           <t>Producto 'Blue Widget' en DB</t>
         </is>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="E116" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process (Gemini devuelve ítem 'Blue Widget')</t>
         </is>
       </c>
-      <c r="F111" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <t>suggested_product_id no es null; suggested_product_name='Blue Widget'.</t>
         </is>
       </c>
-      <c r="G111" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="43.38" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>CP-103</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="43.38" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>CP-108</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>Sin productos en DB no hay sugerencias</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>DB sin productos</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E117" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process</t>
         </is>
       </c>
-      <c r="F112" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <t>Todos los ítems tienen suggested_product_id=null.</t>
         </is>
       </c>
-      <c r="G112" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="37.8" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>CP-104</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="37.8" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>CP-109</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>Proceso requiere autenticación</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>Sin token</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E118" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process sin Authorization</t>
         </is>
       </c>
-      <c r="F113" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <t>HTTP 401.</t>
         </is>
       </c>
-      <c r="G113" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="47.72" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>CP-105</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="47.72" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>CP-110</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
         <is>
           <t>Tipo MIME inválido devuelve 415</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E119" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process {file: doc.txt, MIME: text/plain}</t>
         </is>
       </c>
-      <c r="F114" s="6" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <t>HTTP 415.</t>
-        </is>
-      </c>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="40.28" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>CP-106</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>Facturas (IA)</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>Error de Gemini (JSON inválido) devuelve 422</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>Gemini mock lanza ValueError</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>POST /invoices/process {file: invoice.pdf}</t>
-        </is>
-      </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 422.</t>
-        </is>
-      </c>
-      <c r="G115" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="54.54" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>CP-107</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>Facturas (IA)</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>Confirmar factura con producto existente</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>Factura pendiente, producto 'BW-001' en DB</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>POST /invoices/{id}/confirm {items:[{invoice_item_id, product_id}]}</t>
-        </is>
-      </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 200 — status='confirmed'.</t>
-        </is>
-      </c>
-      <c r="G116" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="41.52" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>CP-108</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>Facturas (IA)</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>Confirmar actualiza el stock del producto</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>Producto con stock=20, factura con ítem qty=10</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>POST /invoices/{id}/confirm</t>
-        </is>
-      </c>
-      <c r="F117" s="6" t="inlineStr">
-        <is>
-          <t>current_stock del producto pasa a 30.</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="59.5" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>CP-109</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>Facturas (IA)</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>Confirmar puede crear producto nuevo inline</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>Factura pendiente, sin productos en DB</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>POST /invoices/{id}/confirm {items:[{..., new_product:{sku, name, price}}]}</t>
-        </is>
-      </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 200 — el nuevo producto aparece en GET /products.</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="65.08" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>CP-110</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>Facturas (IA)</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>Confirmar guarda mapeo SKU proveedor</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>Factura, proveedor y producto en DB</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>POST /invoices/{id}/confirm {supplier_id, items:[{..., supplier_sku:'ACME-BW-XYZ'}]}</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>ProductSupplierMapping creado con supplier_sku='ACME-BW-XYZ'.</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -4686,3422 +4686,3422 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
+          <t>Error de Gemini (JSON inválido) devuelve 422</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>Gemini mock lanza ValueError</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>POST /invoices/process {file: invoice.pdf}</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 422.</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="54.54" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>CP-112</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>Confirmar factura con producto existente</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>Factura pendiente, producto 'BW-001' en DB</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>POST /invoices/{id}/confirm {items:[{invoice_item_id, product_id}]}</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 200 — status='confirmed'.</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="41.52" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>CP-113</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>Confirmar actualiza el stock del producto</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>Producto con stock=20, factura con ítem qty=10</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>POST /invoices/{id}/confirm</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>current_stock del producto pasa a 30.</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="59.5" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>CP-114</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>Confirmar puede crear producto nuevo inline</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>Factura pendiente, sin productos en DB</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>POST /invoices/{id}/confirm {items:[{..., new_product:{sku, name, price}}]}</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 200 — el nuevo producto aparece en GET /products.</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="65.08" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>CP-115</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>Confirmar guarda mapeo SKU proveedor</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Factura, proveedor y producto en DB</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>POST /invoices/{id}/confirm {supplier_id, items:[{..., supplier_sku:'ACME-BW-XYZ'}]}</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>ProductSupplierMapping creado con supplier_sku='ACME-BW-XYZ'.</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40.28" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>CP-116</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
           <t>Confirmar factura ya confirmada devuelve 400</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D125" s="6" t="inlineStr">
         <is>
           <t>Factura en estado confirmed</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E125" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/{id}/confirm nuevamente</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <t>HTTP 400.</t>
         </is>
       </c>
-      <c r="G120" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="37.18" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>CP-112</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="37.18" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>CP-117</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr">
+      <c r="C126" s="6" t="inlineStr">
         <is>
           <t>Rechazar factura pendiente exitosamente</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D126" s="6" t="inlineStr">
         <is>
           <t>Factura en estado pending</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E126" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/{id}/reject</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — status='rejected'.</t>
         </is>
       </c>
-      <c r="G121" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="39.04" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>CP-113</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="39.04" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>CP-118</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C127" s="6" t="inlineStr">
         <is>
           <t>Rechazar factura ya rechazada devuelve 400</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>Factura en estado rejected</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E127" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/{id}/reject nuevamente</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <t>HTTP 400.</t>
         </is>
       </c>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="38.42" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>CP-114</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="38.42" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>CP-119</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>Rechazar factura inexistente devuelve 400</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D128" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E128" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/9999/reject</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <t>HTTP 400 — detail contiene 'not found'.</t>
         </is>
       </c>
-      <c r="G123" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="30.98" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>CP-115</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="30.98" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>CP-120</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C129" s="6" t="inlineStr">
         <is>
           <t>Listar facturas — lista vacía</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D129" s="6" t="inlineStr">
         <is>
           <t>Sin facturas</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E129" s="6" t="inlineStr">
         <is>
           <t>GET /invoices</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — devuelve [].</t>
         </is>
       </c>
-      <c r="G124" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="40.9" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>CP-116</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40.9" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>CP-121</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>Listar facturas devuelve la factura procesada</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D130" s="6" t="inlineStr">
         <is>
           <t>1 factura procesada</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E130" s="6" t="inlineStr">
         <is>
           <t>GET /invoices</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <t>Array de longitud 1.</t>
         </is>
       </c>
-      <c r="G125" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="32.84" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>CP-117</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="32.84" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>CP-122</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr">
         <is>
           <t>Obtener factura por ID</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D131" s="6" t="inlineStr">
         <is>
           <t>1 factura procesada</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E131" s="6" t="inlineStr">
         <is>
           <t>GET /invoices/{id}</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — id coincide, 2 items.</t>
         </is>
       </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="37.8" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>CP-118</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="37.8" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>CP-123</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr">
         <is>
           <t>Obtener factura inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D132" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E132" s="6" t="inlineStr">
         <is>
           <t>GET /invoices/9999</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G127" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="49.58" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>CP-119</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="49.58" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>CP-124</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
         <is>
           <t>Un documento que no es factura se rechaza</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
+      <c r="D133" s="6" t="inlineStr">
         <is>
           <t>Gemini clasifica el documento como no-factura</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E133" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process {file: foto_cualquiera.jpg}</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 — se explica por qué el documento no fue aceptado.</t>
         </is>
       </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="48.34" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>CP-120</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="48.34" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>CP-125</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>Un documento que no es factura no guarda nada</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D134" s="6" t="inlineStr">
         <is>
           <t>Documento rechazado por la IA</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E134" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process y luego GET /invoices</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <t>No se creó ninguna factura ni ítem: la lista sigue vacía.</t>
         </is>
       </c>
-      <c r="G129" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="41.52" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>CP-121</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="41.52" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>CP-126</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
         <is>
           <t>Una factura sin líneas detectables se rechaza</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="D135" s="6" t="inlineStr">
         <is>
           <t>Gemini devuelve 0 ítems</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E135" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process</t>
         </is>
       </c>
-      <c r="F130" s="6" t="inlineStr">
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 — informa que no se detectaron ítems.</t>
         </is>
       </c>
-      <c r="G130" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="55.16" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>CP-122</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="55.16" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>CP-127</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>Archivo con extensión falsificada se rechaza</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr">
+      <c r="D136" s="6" t="inlineStr">
         <is>
           <t>Archivo de texto renombrado a .jpg</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E136" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process {file: fake.jpg}</t>
         </is>
       </c>
-      <c r="F131" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <t>HTTP 415 — se valida el contenido real del archivo, no la extensión.</t>
         </is>
       </c>
-      <c r="G131" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="39.04" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>CP-123</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="39.04" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>CP-128</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C132" s="6" t="inlineStr">
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>Una imagen válida se acepta</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>Imagen real de factura</t>
         </is>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E137" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process {file: factura.png}</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — se procesa normalmente.</t>
         </is>
       </c>
-      <c r="G132" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="57.02" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>CP-124</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="57.02" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>CP-129</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>Línea sin producto asignado da un mensaje de negocio</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>Factura pendiente</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E138" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/{id}/confirm con una línea sin product_id ni new_product</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <t>HTTP 400 — mensaje en español que indica qué línea falta resolver.</t>
         </is>
       </c>
-      <c r="G133" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="50.2" customHeight="1">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>CP-125</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="50.2" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>CP-130</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
+      <c r="C139" s="6" t="inlineStr">
         <is>
           <t>Un producto inexistente no expone su id</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="D139" s="6" t="inlineStr">
         <is>
           <t>Factura pendiente</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E139" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/{id}/confirm {product_id: 9999}</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <t>HTTP 404 sin incluir identificadores internos en el mensaje.</t>
         </is>
       </c>
-      <c r="G134" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="43.38" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>CP-126</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="43.38" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>CP-131</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C140" s="6" t="inlineStr">
         <is>
           <t>Un proveedor inexistente da 404 sin exponer el id</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D140" s="6" t="inlineStr">
         <is>
           <t>Factura pendiente</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E140" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/{id}/confirm {supplier_id: 9999}</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <t>HTTP 404 con mensaje genérico.</t>
         </is>
       </c>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="66.94" customHeight="1">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>CP-127</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="66.94" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>CP-132</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="C141" s="6" t="inlineStr">
         <is>
           <t>La factura sigue pendiente tras un error</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D141" s="6" t="inlineStr">
         <is>
           <t>Confirmación que falla a mitad de camino</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E141" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/{id}/confirm con una línea inválida</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <t>La factura conserva estado 'pending' y el stock no cambia: la operación es todo o nada.</t>
         </is>
       </c>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="62.6" customHeight="1">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>CP-128</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="62.6" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>CP-133</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C142" s="6" t="inlineStr">
         <is>
           <t>Se puede corregir la cantidad extraída por la IA</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D142" s="6" t="inlineStr">
         <is>
           <t>Factura pendiente con cantidad errónea</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E142" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/{id}/confirm enviando una quantity corregida</t>
         </is>
       </c>
-      <c r="F137" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — el stock se actualiza con la cantidad corregida, no con la detectada.</t>
         </is>
       </c>
-      <c r="G137" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="45.24" customHeight="1">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>CP-129</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="45.24" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>CP-134</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C143" s="6" t="inlineStr">
         <is>
           <t>Cantidad decimal rechazada para un producto unitario</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D143" s="6" t="inlineStr">
         <is>
           <t>Producto por unidad</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E143" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/{id}/confirm {quantity:'1.500'}</t>
         </is>
       </c>
-      <c r="F138" s="6" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 — respeta la unidad de medida del producto.</t>
         </is>
       </c>
-      <c r="G138" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="65.08" customHeight="1">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>CP-130</t>
-        </is>
-      </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="65.08" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>CP-135</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="C144" s="6" t="inlineStr">
         <is>
           <t>Un documento ilegible da 422 y no error de servidor</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D144" s="6" t="inlineStr">
         <is>
           <t>Sesión válida; Gemini responde 400 INVALID_ARGUMENT</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="E144" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process con un PDF dañado, vacío o protegido</t>
         </is>
       </c>
-      <c r="F139" s="6" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <t>HTTP 422 con instrucciones para el usuario. El texto de Google no llega al navegador</t>
         </is>
       </c>
-      <c r="G139" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="63.84" customHeight="1">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>CP-131</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="63.84" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>CP-136</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
+      <c r="C145" s="6" t="inlineStr">
         <is>
           <t>La cuota agotada se trata como servicio ocupado</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
+      <c r="D145" s="6" t="inlineStr">
         <is>
           <t>Gemini responde 429 RESOURCE_EXHAUSTED</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="E145" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process</t>
         </is>
       </c>
-      <c r="F140" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <t>HTTP 503 — es un «volvé a intentar», no un archivo mal: el frontend reintenta solo</t>
         </is>
       </c>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="75" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>CP-132</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="75" customHeight="1">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>CP-137</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>Facturas (IA)</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
         <is>
           <t>Las credenciales mal configuradas no culpan al usuario</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D146" s="6" t="inlineStr">
         <is>
           <t>Gemini responde 403 por clave inválida</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E146" s="6" t="inlineStr">
         <is>
           <t>POST /invoices/process</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <t>HTTP 502 y el mensaje no menciona la clave ni pide al usuario que corrija nada: el problema es de configuración</t>
         </is>
       </c>
-      <c r="G141" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="75" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>CP-138</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>El servicio saturado no muestra códigos internos</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>Gemini responde 503 y el reintento automático también falla</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>POST /invoices/process</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>El mensaje está escrito para una persona. Antes viajaba «gemini_unavailable», que es la señal interna para que el frontend reintente</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="75" customHeight="1">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>CP-139</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>Un corte de red no se reporta como falla del sistema</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>La conexión con Google se corta a mitad del pedido</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>POST /invoices/process</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 503, el mismo «volvé a intentar» que la saturación. Un fallo de transporte no es ServerError ni ClientError y llegaba como error 500</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="43.38" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>CP-140</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>Un tiempo de espera agotado recibe el mismo trato</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>La respuesta de Gemini no llega dentro del plazo</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>POST /invoices/process</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 503 y el frontend reintenta solo</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="75" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>CP-141</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>Retomar una revisión conserva el emparejado de la IA</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>Factura pendiente procesada en otro momento</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>GET /invoices/{id} y GET /invoices</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>Las líneas vuelven con su producto sugerido. Se calculaba solo al procesar, así que volver más tarde obligaba a rehacerlo a mano</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="55.16" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>CP-142</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>Una factura ya confirmada no sugiere nada</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>Factura confirmada</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>GET /invoices/{id}</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>Sin sugerencias: la decisión ya está tomada y ofrecerlas confundiría</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="75" customHeight="1">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>CP-143</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>Facturas (IA)</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>Flujo completo con una factura real</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>PDF de proveedor con cuatro líneas y una llamada real a Gemini</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>Subir, revisar y confirmar asociando, creando y omitiendo</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>Se suma el stock de las líneas asociadas, se crea el producto nuevo con su stock inicial y la línea omitida no genera movimiento ni producto</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Clientes</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="40.9" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>CP-133</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
+    <row r="154" ht="40.9" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>CP-144</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
+      <c r="C154" s="6" t="inlineStr">
         <is>
           <t>Crear cliente con todos los campos</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D154" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E154" s="6" t="inlineStr">
         <is>
           <t>POST /customers {name, email, phone, address}</t>
         </is>
       </c>
-      <c r="F143" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — devuelve todos los campos.</t>
         </is>
       </c>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="36.56" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>CP-134</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="36.56" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>CP-145</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
+      <c r="C155" s="6" t="inlineStr">
         <is>
           <t>Crear cliente sin dirección (opcional)</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D155" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E155" s="6" t="inlineStr">
         <is>
           <t>POST /customers {name, email, phone}</t>
         </is>
       </c>
-      <c r="F144" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — address=null.</t>
         </is>
       </c>
-      <c r="G144" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="40.28" customHeight="1">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>CP-135</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="40.28" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>CP-146</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr">
+      <c r="C156" s="6" t="inlineStr">
         <is>
           <t>Crear cliente sin autenticación devuelve 401</t>
         </is>
       </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="D156" s="6" t="inlineStr">
         <is>
           <t>Sin token</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E156" s="6" t="inlineStr">
         <is>
           <t>POST /customers {name, email, phone}</t>
         </is>
       </c>
-      <c r="F145" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <t>HTTP 401.</t>
         </is>
       </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="44.62" customHeight="1">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>CP-136</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="44.62" customHeight="1">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>CP-147</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr">
+      <c r="C157" s="6" t="inlineStr">
         <is>
           <t>Crear cliente con email inválido devuelve 422</t>
         </is>
       </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="D157" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E157" s="6" t="inlineStr">
         <is>
           <t>POST /customers {name, email:'not-an-email', phone}</t>
         </is>
       </c>
-      <c r="F146" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <t>HTTP 422.</t>
         </is>
       </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="30.98" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
-        <is>
-          <t>CP-137</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="30.98" customHeight="1">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>CP-148</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr">
+      <c r="C158" s="6" t="inlineStr">
         <is>
           <t>Listar clientes — lista vacía</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D158" s="6" t="inlineStr">
         <is>
           <t>Sin clientes</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E158" s="6" t="inlineStr">
         <is>
           <t>GET /customers</t>
         </is>
       </c>
-      <c r="F147" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — devuelve [].</t>
         </is>
       </c>
-      <c r="G147" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="31.6" customHeight="1">
-      <c r="A148" s="5" t="inlineStr">
-        <is>
-          <t>CP-138</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="31.6" customHeight="1">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>CP-149</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
         <is>
           <t>Listar clientes devuelve todos</t>
         </is>
       </c>
-      <c r="D148" s="6" t="inlineStr">
+      <c r="D159" s="6" t="inlineStr">
         <is>
           <t>2 clientes en DB</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E159" s="6" t="inlineStr">
         <is>
           <t>GET /customers</t>
         </is>
       </c>
-      <c r="F148" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <t>Array de longitud 2.</t>
         </is>
       </c>
-      <c r="G148" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="39.04" customHeight="1">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>CP-139</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="39.04" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>CP-150</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C149" s="6" t="inlineStr">
+      <c r="C160" s="6" t="inlineStr">
         <is>
           <t>Clientes se devuelven ordenados por nombre</t>
         </is>
       </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="D160" s="6" t="inlineStr">
         <is>
           <t>Clientes 'Zoe' y 'Anna'</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E160" s="6" t="inlineStr">
         <is>
           <t>GET /customers</t>
         </is>
       </c>
-      <c r="F149" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <t>El primer elemento es 'Anna'.</t>
         </is>
       </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="28.5" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>CP-140</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="28.5" customHeight="1">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>CP-151</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C150" s="6" t="inlineStr">
+      <c r="C161" s="6" t="inlineStr">
         <is>
           <t>Obtener cliente existente</t>
         </is>
       </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="D161" s="6" t="inlineStr">
         <is>
           <t>Cliente creado</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E161" s="6" t="inlineStr">
         <is>
           <t>GET /customers/{id}</t>
         </is>
       </c>
-      <c r="F150" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — id coincide.</t>
         </is>
       </c>
-      <c r="G150" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="37.8" customHeight="1">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>CP-141</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="37.8" customHeight="1">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>CP-152</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C151" s="6" t="inlineStr">
+      <c r="C162" s="6" t="inlineStr">
         <is>
           <t>Obtener cliente inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D151" s="6" t="inlineStr">
+      <c r="D162" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E162" s="6" t="inlineStr">
         <is>
           <t>GET /customers/9999</t>
         </is>
       </c>
-      <c r="F151" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="46.48" customHeight="1">
-      <c r="A152" s="5" t="inlineStr">
-        <is>
-          <t>CP-142</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="46.48" customHeight="1">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>CP-153</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C152" s="6" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
         <is>
           <t>Actualizar nombre y teléfono del cliente</t>
         </is>
       </c>
-      <c r="D152" s="6" t="inlineStr">
+      <c r="D163" s="6" t="inlineStr">
         <is>
           <t>Cliente existente</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E163" s="6" t="inlineStr">
         <is>
           <t>PUT /customers/{id} {name:'Updated', phone:'555-9999'}</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — campos actualizados.</t>
         </is>
       </c>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="39.66" customHeight="1">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>CP-143</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="39.66" customHeight="1">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>CP-154</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr">
+      <c r="C164" s="6" t="inlineStr">
         <is>
           <t>Actualizar cliente inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="D164" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E164" s="6" t="inlineStr">
         <is>
           <t>PUT /customers/9999 {name:'Ghost'}</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="36.56" customHeight="1">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>CP-144</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="36.56" customHeight="1">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>CP-155</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C154" s="6" t="inlineStr">
+      <c r="C165" s="6" t="inlineStr">
         <is>
           <t>Eliminar cliente exitosamente</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="D165" s="6" t="inlineStr">
         <is>
           <t>Cliente sin pedidos</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E165" s="6" t="inlineStr">
         <is>
           <t>DELETE /customers/{id}</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <t>HTTP 204 — GET posterior devuelve 404.</t>
         </is>
       </c>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="38.42" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>CP-145</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="38.42" customHeight="1">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>CP-156</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C155" s="6" t="inlineStr">
+      <c r="C166" s="6" t="inlineStr">
         <is>
           <t>Eliminar cliente inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D166" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E166" s="6" t="inlineStr">
         <is>
           <t>DELETE /customers/9999</t>
         </is>
       </c>
-      <c r="F155" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G155" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="39.04" customHeight="1">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>CP-146</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="39.04" customHeight="1">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>CP-157</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C156" s="6" t="inlineStr">
+      <c r="C167" s="6" t="inlineStr">
         <is>
           <t>Historial de pedidos vacío</t>
         </is>
       </c>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="D167" s="6" t="inlineStr">
         <is>
           <t>Cliente sin pedidos</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E167" s="6" t="inlineStr">
         <is>
           <t>GET /customers/{id}/orders</t>
         </is>
       </c>
-      <c r="F156" s="6" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — {customer:{id:...}, orders:[]}.</t>
         </is>
       </c>
-      <c r="G156" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="40.28" customHeight="1">
-      <c r="A157" s="5" t="inlineStr">
-        <is>
-          <t>CP-147</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="40.28" customHeight="1">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>CP-158</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C157" s="6" t="inlineStr">
+      <c r="C168" s="6" t="inlineStr">
         <is>
           <t>Historial incluye pedidos con total correcto</t>
         </is>
       </c>
-      <c r="D157" s="6" t="inlineStr">
+      <c r="D168" s="6" t="inlineStr">
         <is>
           <t>Cliente con 1 pedido de 2 ítems × $10</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E168" s="6" t="inlineStr">
         <is>
           <t>GET /customers/{id}/orders</t>
         </is>
       </c>
-      <c r="F157" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <t>orders tiene 1 elemento con total=20.0.</t>
         </is>
       </c>
-      <c r="G157" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="75" customHeight="1">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>CP-148</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="75" customHeight="1">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>CP-159</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C158" s="6" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
         <is>
           <t>Un cliente con pedidos no se puede eliminar</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="D169" s="6" t="inlineStr">
         <is>
           <t>Cliente con al menos un pedido registrado</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E169" s="6" t="inlineStr">
         <is>
           <t>DELETE /customers/{id}</t>
         </is>
       </c>
-      <c r="F158" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <t>HTTP 409 nombrando los pedidos. Antes el borrado llegaba a la base y volvía como un aviso genérico sobre «información relacionada»</t>
         </is>
       </c>
-      <c r="G158" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="75" customHeight="1">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>CP-149</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="75" customHeight="1">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>CP-160</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
+      <c r="C170" s="6" t="inlineStr">
         <is>
           <t>El listado avisa por adelantado que no se puede borrar</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="D170" s="6" t="inlineStr">
         <is>
           <t>Un cliente con pedidos y otro sin ellos</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E170" s="6" t="inlineStr">
         <is>
           <t>GET /customers</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <t>can_delete=false y el motivo en el cliente con pedidos, para deshabilitar el botón en vez de fallar al confirmarlo</t>
         </is>
       </c>
-      <c r="G159" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="4" t="inlineStr">
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Pedidos</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="43.38" customHeight="1">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>CP-150</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
+    <row r="172" ht="43.38" customHeight="1">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>CP-161</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
+      <c r="C172" s="6" t="inlineStr">
         <is>
           <t>Crear pedido exitosamente</t>
         </is>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D172" s="6" t="inlineStr">
         <is>
           <t>Cliente en DB</t>
         </is>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E172" s="6" t="inlineStr">
         <is>
           <t>POST /orders {customer_id}</t>
         </is>
       </c>
-      <c r="F161" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <t>HTTP 201 — status='pending', items=[], total=0.0.</t>
         </is>
       </c>
-      <c r="G161" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="43.38" customHeight="1">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>CP-151</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="43.38" customHeight="1">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>CP-162</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
+      <c r="C173" s="6" t="inlineStr">
         <is>
           <t>Crear pedido con cliente inexistente devuelve 400</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="D173" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E173" s="6" t="inlineStr">
         <is>
           <t>POST /orders {customer_id:9999}</t>
         </is>
       </c>
-      <c r="F162" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <t>HTTP 400 — detail contiene 'not found'.</t>
         </is>
       </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="39.66" customHeight="1">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>CP-152</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="39.66" customHeight="1">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>CP-163</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C163" s="6" t="inlineStr">
+      <c r="C174" s="6" t="inlineStr">
         <is>
           <t>Crear pedido sin autenticación devuelve 401</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D174" s="6" t="inlineStr">
         <is>
           <t>Sin token</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E174" s="6" t="inlineStr">
         <is>
           <t>POST /orders {customer_id}</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <t>HTTP 401.</t>
         </is>
       </c>
-      <c r="G163" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="30.36" customHeight="1">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>CP-153</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="30.36" customHeight="1">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>CP-164</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C164" s="6" t="inlineStr">
+      <c r="C175" s="6" t="inlineStr">
         <is>
           <t>Listar pedidos — lista vacía</t>
         </is>
       </c>
-      <c r="D164" s="6" t="inlineStr">
+      <c r="D175" s="6" t="inlineStr">
         <is>
           <t>Sin pedidos</t>
         </is>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="E175" s="6" t="inlineStr">
         <is>
           <t>GET /orders</t>
         </is>
       </c>
-      <c r="F164" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — devuelve [].</t>
         </is>
       </c>
-      <c r="G164" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="33.46" customHeight="1">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>CP-154</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="33.46" customHeight="1">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>CP-165</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C165" s="6" t="inlineStr">
+      <c r="C176" s="6" t="inlineStr">
         <is>
           <t>Listar pedidos devuelve el creado</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D176" s="6" t="inlineStr">
         <is>
           <t>1 pedido en DB</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E176" s="6" t="inlineStr">
         <is>
           <t>GET /orders</t>
         </is>
       </c>
-      <c r="F165" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <t>Array de longitud 1.</t>
         </is>
       </c>
-      <c r="G165" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="27.88" customHeight="1">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>CP-155</t>
-        </is>
-      </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="27.88" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>CP-166</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
+      <c r="C177" s="6" t="inlineStr">
         <is>
           <t>Obtener pedido existente</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="D177" s="6" t="inlineStr">
         <is>
           <t>Pedido creado</t>
         </is>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="E177" s="6" t="inlineStr">
         <is>
           <t>GET /orders/{id}</t>
         </is>
       </c>
-      <c r="F166" s="6" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — id coincide.</t>
         </is>
       </c>
-      <c r="G166" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="37.18" customHeight="1">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>CP-156</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="37.18" customHeight="1">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>CP-167</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C167" s="6" t="inlineStr">
+      <c r="C178" s="6" t="inlineStr">
         <is>
           <t>Obtener pedido inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D167" s="6" t="inlineStr">
+      <c r="D178" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E178" s="6" t="inlineStr">
         <is>
           <t>GET /orders/9999</t>
         </is>
       </c>
-      <c r="F167" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G167" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="52.68" customHeight="1">
-      <c r="A168" s="5" t="inlineStr">
-        <is>
-          <t>CP-157</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="52.68" customHeight="1">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>CP-168</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C168" s="6" t="inlineStr">
+      <c r="C179" s="6" t="inlineStr">
         <is>
           <t>Agregar ítem a pedido pendiente</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D179" s="6" t="inlineStr">
         <is>
           <t>Pedido pending, producto con stock=100</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E179" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/items {product_id, qty:'3.000', price:'10.00'}</t>
         </is>
       </c>
-      <c r="F168" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — items tiene 1 elemento, total=30.0.</t>
         </is>
       </c>
-      <c r="G168" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="42.76" customHeight="1">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>CP-158</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="42.76" customHeight="1">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>CP-169</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C169" s="6" t="inlineStr">
+      <c r="C180" s="6" t="inlineStr">
         <is>
           <t>Agregar ítem con stock insuficiente devuelve 400</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="D180" s="6" t="inlineStr">
         <is>
           <t>Producto con stock=2</t>
         </is>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="E180" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/items {qty:'10.000'}</t>
         </is>
       </c>
-      <c r="F169" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <t>HTTP 400 — detail contiene 'insufficient'.</t>
         </is>
       </c>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="41.52" customHeight="1">
-      <c r="A170" s="5" t="inlineStr">
-        <is>
-          <t>CP-159</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="41.52" customHeight="1">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>CP-170</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C170" s="6" t="inlineStr">
+      <c r="C181" s="6" t="inlineStr">
         <is>
           <t>Agregar ítem de producto inactivo devuelve 400</t>
         </is>
       </c>
-      <c r="D170" s="6" t="inlineStr">
+      <c r="D181" s="6" t="inlineStr">
         <is>
           <t>Producto inactivo (is_active=False)</t>
         </is>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="E181" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/items</t>
         </is>
       </c>
-      <c r="F170" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <t>HTTP 400.</t>
         </is>
       </c>
-      <c r="G170" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="41.52" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>CP-160</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="41.52" customHeight="1">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>CP-171</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C171" s="6" t="inlineStr">
+      <c r="C182" s="6" t="inlineStr">
         <is>
           <t>Agregar ítem a pedido inexistente devuelve 400</t>
         </is>
       </c>
-      <c r="D171" s="6" t="inlineStr">
+      <c r="D182" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E182" s="6" t="inlineStr">
         <is>
           <t>POST /orders/9999/items</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <t>HTTP 400 — detail contiene 'not found'.</t>
         </is>
       </c>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="34.7" customHeight="1">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t>CP-161</t>
-        </is>
-      </c>
-      <c r="B172" s="6" t="inlineStr">
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="34.7" customHeight="1">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>CP-172</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C172" s="6" t="inlineStr">
+      <c r="C183" s="6" t="inlineStr">
         <is>
           <t>Eliminar ítem de pedido pendiente</t>
         </is>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D183" s="6" t="inlineStr">
         <is>
           <t>Pedido con 1 ítem</t>
         </is>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="E183" s="6" t="inlineStr">
         <is>
           <t>DELETE /orders/{id}/items/{item_id}</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — items=[].</t>
         </is>
       </c>
-      <c r="G172" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="36.56" customHeight="1">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>CP-162</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="36.56" customHeight="1">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>CP-173</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C173" s="6" t="inlineStr">
+      <c r="C184" s="6" t="inlineStr">
         <is>
           <t>Eliminar pedido pendiente exitosamente</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D184" s="6" t="inlineStr">
         <is>
           <t>Pedido en estado pending</t>
         </is>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="E184" s="6" t="inlineStr">
         <is>
           <t>DELETE /orders/{id}</t>
         </is>
       </c>
-      <c r="F173" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <t>HTTP 204.</t>
         </is>
       </c>
-      <c r="G173" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="37.18" customHeight="1">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>CP-163</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="37.18" customHeight="1">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>CP-174</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C174" s="6" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
         <is>
           <t>Eliminar pedido no-pending devuelve 400</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>Pedido en estado processing</t>
         </is>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E185" s="6" t="inlineStr">
         <is>
           <t>DELETE /orders/{id}</t>
         </is>
       </c>
-      <c r="F174" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <t>HTTP 400.</t>
         </is>
       </c>
-      <c r="G174" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="50.82" customHeight="1">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>CP-164</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="50.82" customHeight="1">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>CP-175</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C175" s="6" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
         <is>
           <t>Avanzar pending→processing descuenta stock</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t>Pedido con 1 ítem qty=5, producto stock=100</t>
         </is>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E186" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/advance</t>
         </is>
       </c>
-      <c r="F175" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — status='processing'; stock del producto pasa a 95.</t>
         </is>
       </c>
-      <c r="G175" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="52.68" customHeight="1">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>CP-165</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="52.68" customHeight="1">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>CP-176</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C176" s="6" t="inlineStr">
+      <c r="C187" s="6" t="inlineStr">
         <is>
           <t>Avanzar pending→processing crea movimiento de salida</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>Pedido con ítem qty=3</t>
         </is>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E187" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/advance</t>
         </is>
       </c>
-      <c r="F176" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <t>StockMovement de tipo 'exit' con quantity=3 y order_id correcto.</t>
         </is>
       </c>
-      <c r="G176" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="50.2" customHeight="1">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>CP-166</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="50.2" customHeight="1">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>CP-177</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
         <is>
           <t>Ciclo completo: pending→processing→shipped→delivered</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>Pedido con 1 ítem, stock suficiente</t>
         </is>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>3 × POST /orders/{id}/advance</t>
         </is>
       </c>
-      <c r="F177" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <t>Statuses secuenciales: ['processing','shipped','delivered'].</t>
         </is>
       </c>
-      <c r="G177" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="37.8" customHeight="1">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>CP-167</t>
-        </is>
-      </c>
-      <c r="B178" s="6" t="inlineStr">
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="37.8" customHeight="1">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>CP-178</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C178" s="6" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
         <is>
           <t>Avanzar pedido ya entregado devuelve 400</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>Pedido en estado delivered</t>
         </is>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="E189" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/advance</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <t>HTTP 400.</t>
         </is>
       </c>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="36.56" customHeight="1">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>CP-168</t>
-        </is>
-      </c>
-      <c r="B179" s="6" t="inlineStr">
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="36.56" customHeight="1">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>CP-179</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
+      <c r="C190" s="6" t="inlineStr">
         <is>
           <t>Avanzar pedido vacío devuelve 400</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>Pedido sin ítems</t>
         </is>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E190" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/advance</t>
         </is>
       </c>
-      <c r="F179" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <t>HTTP 400 — detail contiene 'no items'.</t>
         </is>
       </c>
-      <c r="G179" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="53.92" customHeight="1">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>CP-169</t>
-        </is>
-      </c>
-      <c r="B180" s="6" t="inlineStr">
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="53.92" customHeight="1">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>CP-180</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C180" s="6" t="inlineStr">
+      <c r="C191" s="6" t="inlineStr">
         <is>
           <t>Avanzar con stock insuficiente al momento de procesar devuelve 400</t>
         </is>
       </c>
-      <c r="D180" s="6" t="inlineStr">
+      <c r="D191" s="6" t="inlineStr">
         <is>
           <t>Pedido con ítem qty=5, stock drenado a 0 manualmente</t>
         </is>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E191" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/advance</t>
         </is>
       </c>
-      <c r="F180" s="6" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <t>HTTP 400. El pedido permanece en 'pending'.</t>
         </is>
       </c>
-      <c r="G180" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="75" customHeight="1">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t>CP-170</t>
-        </is>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="75" customHeight="1">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>CP-181</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr">
+      <c r="C192" s="6" t="inlineStr">
         <is>
           <t>El mismo producto en dos líneas no supera el stock</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D192" s="6" t="inlineStr">
         <is>
           <t>Producto con 3 unidades; una línea ya reserva 2</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E192" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/items con 2 unidades más del mismo producto</t>
         </is>
       </c>
-      <c r="F181" s="6" t="inlineStr">
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <t>HTTP 400: el mensaje aclara que el pedido ya reserva 2, si no el stock a secas (3) parecería alcanzar para la línea que se pide</t>
         </is>
       </c>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="75" customHeight="1">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>CP-171</t>
-        </is>
-      </c>
-      <c r="B182" s="6" t="inlineStr">
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="75" customHeight="1">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>CP-182</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C182" s="6" t="inlineStr">
+      <c r="C193" s="6" t="inlineStr">
         <is>
           <t>Al confirmar se informa el stock real, no uno intermedio</t>
         </is>
       </c>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="D193" s="6" t="inlineStr">
         <is>
           <t>Pedido con dos líneas de 1 unidad de un producto que tiene 1</t>
         </is>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E193" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/advance</t>
         </is>
       </c>
-      <c r="F182" s="6" t="inlineStr">
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <t>«quedan 1 y el pedido requiere 2». Antes validaba mientras descontaba y decía «quedan 0», un número que no coincidía con el que muestra la pantalla de productos</t>
         </is>
       </c>
-      <c r="G182" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="75" customHeight="1">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>CP-172</t>
-        </is>
-      </c>
-      <c r="B183" s="6" t="inlineStr">
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="75" customHeight="1">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>CP-183</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C183" s="6" t="inlineStr">
+      <c r="C194" s="6" t="inlineStr">
         <is>
           <t>El pedido avanza si la suma de las líneas entra en el stock</t>
         </is>
       </c>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="D194" s="6" t="inlineStr">
         <is>
           <t>Producto con 5 unidades y dos líneas de 2</t>
         </is>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="E194" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/advance</t>
         </is>
       </c>
-      <c r="F183" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 y el stock queda en 1: agrupar por producto no debe bloquear pedidos que sí se pueden cumplir</t>
         </is>
       </c>
-      <c r="G183" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="75" customHeight="1">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>CP-173</t>
-        </is>
-      </c>
-      <c r="B184" s="6" t="inlineStr">
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="75" customHeight="1">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>CP-184</t>
+        </is>
+      </c>
+      <c r="B195" s="6" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C184" s="6" t="inlineStr">
+      <c r="C195" s="6" t="inlineStr">
         <is>
           <t>Las cantidades redondas grandes se leen como números</t>
         </is>
       </c>
-      <c r="D184" s="6" t="inlineStr">
+      <c r="D195" s="6" t="inlineStr">
         <is>
           <t>Producto con 1000 unidades</t>
         </is>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E195" s="6" t="inlineStr">
         <is>
           <t>POST /orders/{id}/items pidiendo 2000</t>
         </is>
       </c>
-      <c r="F184" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <t>El mensaje dice «quedan 1000» y no «quedan 1E+3»: la notación científica aparecía sola al quitar los ceros de relleno</t>
         </is>
       </c>
-      <c r="G184" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="A196" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Movimientos de Stock</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="40.28" customHeight="1">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>CP-174</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
+    <row r="197" ht="40.28" customHeight="1">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>CP-185</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
+      <c r="C197" s="6" t="inlineStr">
         <is>
           <t>Listar movimientos — vacío sin stock inicial</t>
         </is>
       </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="D197" s="6" t="inlineStr">
         <is>
           <t>Producto creado con stock=0</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E197" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — devuelve [].</t>
         </is>
       </c>
-      <c r="G186" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="50.2" customHeight="1">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>CP-175</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="50.2" customHeight="1">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>CP-186</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
+      <c r="C198" s="6" t="inlineStr">
         <is>
           <t>Producto con stock&gt;0 genera movimiento de entrada al crearse</t>
         </is>
       </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D198" s="6" t="inlineStr">
         <is>
           <t>Producto con stock=50</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E198" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <t>1 movimiento de tipo 'entry'.</t>
         </is>
       </c>
-      <c r="G187" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="38.42" customHeight="1">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>CP-176</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="38.42" customHeight="1">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>CP-187</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
+      <c r="C199" s="6" t="inlineStr">
         <is>
           <t>Filtro por tipo=entry</t>
         </is>
       </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="D199" s="6" t="inlineStr">
         <is>
           <t>1 movimiento de entrada</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E199" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements?type=entry</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <t>Todos los resultados tienen type='entry'.</t>
         </is>
       </c>
-      <c r="G188" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="42.76" customHeight="1">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>CP-177</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="42.76" customHeight="1">
+      <c r="A200" s="5" t="inlineStr">
+        <is>
+          <t>CP-188</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
+      <c r="C200" s="6" t="inlineStr">
         <is>
           <t>Filtro por tipo=exit — sin ventas devuelve vacío</t>
         </is>
       </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="D200" s="6" t="inlineStr">
         <is>
           <t>Solo hay movimientos de entrada</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E200" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements?type=exit</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <t>Devuelve [].</t>
         </is>
       </c>
-      <c r="G189" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="47.1" customHeight="1">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>CP-178</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="47.1" customHeight="1">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>CP-189</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
+      <c r="C201" s="6" t="inlineStr">
         <is>
           <t>Filtro por tipo=adjustment tras edición manual de stock</t>
         </is>
       </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="D201" s="6" t="inlineStr">
         <is>
           <t>Producto actualizado manualmente (stock 50→60)</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E201" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements?type=adjustment</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <t>1 movimiento de tipo 'adjustment'.</t>
         </is>
       </c>
-      <c r="G190" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="42.76" customHeight="1">
-      <c r="A191" s="5" t="inlineStr">
-        <is>
-          <t>CP-179</t>
-        </is>
-      </c>
-      <c r="B191" s="6" t="inlineStr">
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="42.76" customHeight="1">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>CP-190</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C191" s="6" t="inlineStr">
+      <c r="C202" s="6" t="inlineStr">
         <is>
           <t>Filtro por product_id filtra correctamente</t>
         </is>
       </c>
-      <c r="D191" s="6" t="inlineStr">
+      <c r="D202" s="6" t="inlineStr">
         <is>
           <t>2 productos con movimientos</t>
         </is>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E202" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements?product_id={p1.id}</t>
         </is>
       </c>
-      <c r="F191" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <t>Todos los movimientos pertenecen al producto p1.</t>
         </is>
       </c>
-      <c r="G191" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="50.2" customHeight="1">
-      <c r="A192" s="5" t="inlineStr">
-        <is>
-          <t>CP-180</t>
-        </is>
-      </c>
-      <c r="B192" s="6" t="inlineStr">
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="50.2" customHeight="1">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>CP-191</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C192" s="6" t="inlineStr">
+      <c r="C203" s="6" t="inlineStr">
         <is>
           <t>Filtro por rango de fechas</t>
         </is>
       </c>
-      <c r="D192" s="6" t="inlineStr">
+      <c r="D203" s="6" t="inlineStr">
         <is>
           <t>1 movimiento existente</t>
         </is>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E203" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements?date_from=2020-01-01&amp;date_to=2099-12-31</t>
         </is>
       </c>
-      <c r="F192" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — al menos 1 resultado.</t>
         </is>
       </c>
-      <c r="G192" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="37.8" customHeight="1">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>CP-181</t>
-        </is>
-      </c>
-      <c r="B193" s="6" t="inlineStr">
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="37.8" customHeight="1">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>CP-192</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C193" s="6" t="inlineStr">
+      <c r="C204" s="6" t="inlineStr">
         <is>
           <t>Paginación con limit=3</t>
         </is>
       </c>
-      <c r="D193" s="6" t="inlineStr">
+      <c r="D204" s="6" t="inlineStr">
         <is>
           <t>5 productos creados (5 movimientos)</t>
         </is>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E204" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements?limit=3</t>
         </is>
       </c>
-      <c r="F193" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — array de 3 o menos elementos.</t>
         </is>
       </c>
-      <c r="G193" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="38.42" customHeight="1">
-      <c r="A194" s="5" t="inlineStr">
-        <is>
-          <t>CP-182</t>
-        </is>
-      </c>
-      <c r="B194" s="6" t="inlineStr">
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="38.42" customHeight="1">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>CP-193</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C194" s="6" t="inlineStr">
+      <c r="C205" s="6" t="inlineStr">
         <is>
           <t>Listar movimientos requiere autenticación</t>
         </is>
       </c>
-      <c r="D194" s="6" t="inlineStr">
+      <c r="D205" s="6" t="inlineStr">
         <is>
           <t>Sin token</t>
         </is>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="E205" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements</t>
         </is>
       </c>
-      <c r="F194" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <t>HTTP 401.</t>
         </is>
       </c>
-      <c r="G194" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="35.94" customHeight="1">
-      <c r="A195" s="5" t="inlineStr">
-        <is>
-          <t>CP-183</t>
-        </is>
-      </c>
-      <c r="B195" s="6" t="inlineStr">
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="35.94" customHeight="1">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>CP-194</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C195" s="6" t="inlineStr">
+      <c r="C206" s="6" t="inlineStr">
         <is>
           <t>Obtener movimiento por ID existente</t>
         </is>
       </c>
-      <c r="D195" s="6" t="inlineStr">
+      <c r="D206" s="6" t="inlineStr">
         <is>
           <t>Movimiento en DB</t>
         </is>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E206" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements/{id}</t>
         </is>
       </c>
-      <c r="F195" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — id coincide, type='entry'.</t>
         </is>
       </c>
-      <c r="G195" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="39.66" customHeight="1">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>CP-184</t>
-        </is>
-      </c>
-      <c r="B196" s="6" t="inlineStr">
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="39.66" customHeight="1">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>CP-195</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C196" s="6" t="inlineStr">
+      <c r="C207" s="6" t="inlineStr">
         <is>
           <t>Obtener movimiento inexistente devuelve 404</t>
         </is>
       </c>
-      <c r="D196" s="6" t="inlineStr">
+      <c r="D207" s="6" t="inlineStr">
         <is>
           <t>DB vacía</t>
         </is>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E207" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements/9999</t>
         </is>
       </c>
-      <c r="F196" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <t>HTTP 404.</t>
         </is>
       </c>
-      <c r="G196" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="41.52" customHeight="1">
-      <c r="A197" s="5" t="inlineStr">
-        <is>
-          <t>CP-185</t>
-        </is>
-      </c>
-      <c r="B197" s="6" t="inlineStr">
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="41.52" customHeight="1">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>CP-196</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C197" s="6" t="inlineStr">
+      <c r="C208" s="6" t="inlineStr">
         <is>
           <t>Movimiento de salida queda vinculado al pedido</t>
         </is>
       </c>
-      <c r="D197" s="6" t="inlineStr">
+      <c r="D208" s="6" t="inlineStr">
         <is>
           <t>Pedido avanzado a 'processing'</t>
         </is>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E208" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements/{exit_movement_id}</t>
         </is>
       </c>
-      <c r="F197" s="6" t="inlineStr">
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — order_id coincide con el pedido.</t>
         </is>
       </c>
-      <c r="G197" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="60.74" customHeight="1">
-      <c r="A198" s="5" t="inlineStr">
-        <is>
-          <t>CP-186</t>
-        </is>
-      </c>
-      <c r="B198" s="6" t="inlineStr">
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="60.74" customHeight="1">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>CP-197</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C198" s="6" t="inlineStr">
+      <c r="C209" s="6" t="inlineStr">
         <is>
           <t>Rango de fechas invertido da error con mensaje claro</t>
         </is>
       </c>
-      <c r="D198" s="6" t="inlineStr">
+      <c r="D209" s="6" t="inlineStr">
         <is>
           <t>Movimientos registrados</t>
         </is>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E209" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements?date_from=2026-05-01&amp;date_to=2026-01-01</t>
         </is>
       </c>
-      <c r="F198" s="6" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <t>HTTP 400/422 con un mensaje explicativo, en lugar de una lista vacía ambigua.</t>
         </is>
       </c>
-      <c r="G198" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="40.9" customHeight="1">
-      <c r="A199" s="5" t="inlineStr">
-        <is>
-          <t>CP-187</t>
-        </is>
-      </c>
-      <c r="B199" s="6" t="inlineStr">
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40.9" customHeight="1">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>CP-198</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C199" s="6" t="inlineStr">
+      <c r="C210" s="6" t="inlineStr">
         <is>
           <t>Fecha 'desde' en el futuro da error</t>
         </is>
       </c>
-      <c r="D199" s="6" t="inlineStr">
+      <c r="D210" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="E210" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements?date_from=&lt;fecha futura&gt;</t>
         </is>
       </c>
-      <c r="F199" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <t>HTTP 400/422 con el motivo.</t>
         </is>
       </c>
-      <c r="G199" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="42.14" customHeight="1">
-      <c r="A200" s="5" t="inlineStr">
-        <is>
-          <t>CP-188</t>
-        </is>
-      </c>
-      <c r="B200" s="6" t="inlineStr">
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="42.14" customHeight="1">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>CP-199</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C200" s="6" t="inlineStr">
+      <c r="C211" s="6" t="inlineStr">
         <is>
           <t>Un 'hasta' lejano es válido</t>
         </is>
       </c>
-      <c r="D200" s="6" t="inlineStr">
+      <c r="D211" s="6" t="inlineStr">
         <is>
           <t>Movimientos registrados</t>
         </is>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E211" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements?date_to=2099-12-31</t>
         </is>
       </c>
-      <c r="F200" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — devuelve los movimientos existentes.</t>
         </is>
       </c>
-      <c r="G200" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="42.14" customHeight="1">
-      <c r="A201" s="5" t="inlineStr">
-        <is>
-          <t>CP-189</t>
-        </is>
-      </c>
-      <c r="B201" s="6" t="inlineStr">
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="42.14" customHeight="1">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>CP-200</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C201" s="6" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
         <is>
           <t>Un rango con extremos iguales es válido</t>
         </is>
       </c>
-      <c r="D201" s="6" t="inlineStr">
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>Movimientos del día</t>
         </is>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="E212" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements?date_from=X&amp;date_to=X</t>
         </is>
       </c>
-      <c r="F201" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <t>HTTP 200 — el rango de un solo día es aceptado.</t>
         </is>
       </c>
-      <c r="G201" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="75" customHeight="1">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>CP-190</t>
-        </is>
-      </c>
-      <c r="B202" s="6" t="inlineStr">
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="75" customHeight="1">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>CP-201</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C202" s="6" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
         <is>
           <t>El detalle marca las líneas omitidas de la factura</t>
         </is>
       </c>
-      <c r="D202" s="6" t="inlineStr">
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>Factura confirmada con una línea asociada y otra omitida</t>
         </is>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="E213" s="6" t="inlineStr">
         <is>
           <t>GET /stock-movements/{id} del movimiento generado</t>
         </is>
       </c>
-      <c r="F202" s="6" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <t>La línea omitida viaja con skipped=true. Sin ese campo la pantalla de trazabilidad la mostraba como «Sumada al stock»</t>
         </is>
       </c>
-      <c r="G202" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="75" customHeight="1">
-      <c r="A203" s="5" t="inlineStr">
-        <is>
-          <t>CP-191</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
+      <c r="G213" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="75" customHeight="1">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>CP-202</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C203" s="6" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
         <is>
           <t>Las tablas avisan cuando quedan columnas fuera de pantalla</t>
         </is>
       </c>
-      <c r="D203" s="6" t="inlineStr">
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>Pantalla angosta (teléfono) con la tabla más ancha que el visor</t>
         </is>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E214" s="6" t="inlineStr">
         <is>
           <t>Abrir el listado y desplazarlo horizontalmente</t>
         </is>
       </c>
-      <c r="F203" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <t>Aparece una sombra en el borde con contenido oculto y desaparece al llegar al final. Sin esa señal, desde el teléfono el listado parecía no tener botones de acción</t>
         </is>
       </c>
-      <c r="G203" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="18" customHeight="1">
-      <c r="A204" s="4" t="inlineStr">
+      <c r="G214" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="A215" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Aislamiento multi-tenant</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="74.38" customHeight="1">
-      <c r="A205" s="5" t="inlineStr">
-        <is>
-          <t>CP-192</t>
-        </is>
-      </c>
-      <c r="B205" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C205" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de productos: no se listan los de otra organización</t>
-        </is>
-      </c>
-      <c r="D205" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E205" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre productos de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F205" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
-        </is>
-      </c>
-      <c r="G205" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="74.38" customHeight="1">
-      <c r="A206" s="5" t="inlineStr">
-        <is>
-          <t>CP-193</t>
-        </is>
-      </c>
-      <c r="B206" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C206" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de productos: no se accede por id a uno ajeno</t>
-        </is>
-      </c>
-      <c r="D206" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E206" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre productos de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F206" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
-        </is>
-      </c>
-      <c r="G206" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="74.38" customHeight="1">
-      <c r="A207" s="5" t="inlineStr">
-        <is>
-          <t>CP-194</t>
-        </is>
-      </c>
-      <c r="B207" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C207" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de productos: no se modifica uno ajeno</t>
-        </is>
-      </c>
-      <c r="D207" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E207" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre productos de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F207" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
-        </is>
-      </c>
-      <c r="G207" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="74.38" customHeight="1">
-      <c r="A208" s="5" t="inlineStr">
-        <is>
-          <t>CP-195</t>
-        </is>
-      </c>
-      <c r="B208" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C208" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de productos: no se elimina uno ajeno</t>
-        </is>
-      </c>
-      <c r="D208" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E208" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre productos de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F208" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
-        </is>
-      </c>
-      <c r="G208" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="74.38" customHeight="1">
-      <c r="A209" s="5" t="inlineStr">
-        <is>
-          <t>CP-196</t>
-        </is>
-      </c>
-      <c r="B209" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C209" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de proveedores: no se listan los de otra organización</t>
-        </is>
-      </c>
-      <c r="D209" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E209" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre proveedores de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F209" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
-        </is>
-      </c>
-      <c r="G209" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="74.38" customHeight="1">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>CP-197</t>
-        </is>
-      </c>
-      <c r="B210" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C210" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de proveedores: no se accede a uno ajeno</t>
-        </is>
-      </c>
-      <c r="D210" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E210" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre proveedores de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F210" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
-        </is>
-      </c>
-      <c r="G210" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="74.38" customHeight="1">
-      <c r="A211" s="5" t="inlineStr">
-        <is>
-          <t>CP-198</t>
-        </is>
-      </c>
-      <c r="B211" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C211" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de clientes: no se listan los de otra organización</t>
-        </is>
-      </c>
-      <c r="D211" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E211" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre clientes de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F211" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
-        </is>
-      </c>
-      <c r="G211" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="74.38" customHeight="1">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>CP-199</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C212" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de clientes: no se accede a uno ajeno</t>
-        </is>
-      </c>
-      <c r="D212" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E212" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre clientes de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
-        </is>
-      </c>
-      <c r="G212" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="60.74" customHeight="1">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>CP-200</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de clientes: el mismo correo puede repetirse en otra organización</t>
-        </is>
-      </c>
-      <c r="D213" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E213" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre clientes de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 201 — la unicidad es por organización.</t>
-        </is>
-      </c>
-      <c r="G213" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="74.38" customHeight="1">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>CP-201</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C214" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de clientes: no se ve el historial de pedidos de un cliente ajeno</t>
-        </is>
-      </c>
-      <c r="D214" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E214" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre clientes de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
-        </is>
-      </c>
-      <c r="G214" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="74.38" customHeight="1">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>CP-202</t>
-        </is>
-      </c>
-      <c r="B215" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento multi-tenant</t>
-        </is>
-      </c>
-      <c r="C215" s="6" t="inlineStr">
-        <is>
-          <t>Aislamiento de facturas: no se listan las de otra organización</t>
-        </is>
-      </c>
-      <c r="D215" s="6" t="inlineStr">
-        <is>
-          <t>Dos organizaciones (A y B) con datos propios</t>
-        </is>
-      </c>
-      <c r="E215" s="6" t="inlineStr">
-        <is>
-          <t>Petición sobre facturas de la organización B usando el token de A</t>
-        </is>
-      </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
-        </is>
-      </c>
-      <c r="G215" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>Aislamiento de facturas: no se accede a una ajena</t>
+          <t>Aislamiento de productos: no se listan los de otra organización</t>
         </is>
       </c>
       <c r="D216" s="6" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Petición sobre facturas de la organización B usando el token de A</t>
+          <t>Petición sobre productos de la organización B usando el token de A</t>
         </is>
       </c>
       <c r="F216" s="6" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>Aislamiento de facturas: no se confirma una ajena</t>
+          <t>Aislamiento de productos: no se accede por id a uno ajeno</t>
         </is>
       </c>
       <c r="D217" s="6" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Petición sobre facturas de la organización B usando el token de A</t>
+          <t>Petición sobre productos de la organización B usando el token de A</t>
         </is>
       </c>
       <c r="F217" s="6" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>Aislamiento de facturas: no se sugieren productos de otra organización</t>
+          <t>Aislamiento de productos: no se modifica uno ajeno</t>
         </is>
       </c>
       <c r="D218" s="6" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Petición sobre facturas de la organización B usando el token de A</t>
+          <t>Petición sobre productos de la organización B usando el token de A</t>
         </is>
       </c>
       <c r="F218" s="6" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>Aislamiento de pedidos: no se listan los de otra organización</t>
+          <t>Aislamiento de productos: no se elimina uno ajeno</t>
         </is>
       </c>
       <c r="D219" s="6" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Petición sobre pedidos de la organización B usando el token de A</t>
+          <t>Petición sobre productos de la organización B usando el token de A</t>
         </is>
       </c>
       <c r="F219" s="6" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>Aislamiento de pedidos: no se accede a uno ajeno</t>
+          <t>Aislamiento de proveedores: no se listan los de otra organización</t>
         </is>
       </c>
       <c r="D220" s="6" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Petición sobre pedidos de la organización B usando el token de A</t>
+          <t>Petición sobre proveedores de la organización B usando el token de A</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>Aislamiento de pedidos: no se avanza el estado de uno ajeno</t>
+          <t>Aislamiento de proveedores: no se accede a uno ajeno</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Petición sobre pedidos de la organización B usando el token de A</t>
+          <t>Petición sobre proveedores de la organización B usando el token de A</t>
         </is>
       </c>
       <c r="F221" s="6" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>Aislamiento de pedidos: no se usa un cliente de otra organización</t>
+          <t>Aislamiento de clientes: no se listan los de otra organización</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Petición sobre pedidos de la organización B usando el token de A</t>
+          <t>Petición sobre clientes de la organización B usando el token de A</t>
         </is>
       </c>
       <c r="F222" s="6" t="inlineStr">
@@ -8377,89 +8377,496 @@
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
+          <t>Aislamiento de clientes: no se accede a uno ajeno</t>
+        </is>
+      </c>
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre clientes de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F223" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="60.74" customHeight="1">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
+          <t>CP-211</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento de clientes: el mismo correo puede repetirse en otra organización</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre clientes de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 201 — la unicidad es por organización.</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="74.38" customHeight="1">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>CP-212</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento de clientes: no se ve el historial de pedidos de un cliente ajeno</t>
+        </is>
+      </c>
+      <c r="D225" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre clientes de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="74.38" customHeight="1">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>CP-213</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento de facturas: no se listan las de otra organización</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre facturas de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="74.38" customHeight="1">
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t>CP-214</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento de facturas: no se accede a una ajena</t>
+        </is>
+      </c>
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre facturas de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="74.38" customHeight="1">
+      <c r="A228" s="5" t="inlineStr">
+        <is>
+          <t>CP-215</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento de facturas: no se confirma una ajena</t>
+        </is>
+      </c>
+      <c r="D228" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre facturas de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="74.38" customHeight="1">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>CP-216</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento de facturas: no se sugieren productos de otra organización</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre facturas de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F229" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="74.38" customHeight="1">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t>CP-217</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento de pedidos: no se listan los de otra organización</t>
+        </is>
+      </c>
+      <c r="D230" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre pedidos de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="74.38" customHeight="1">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>CP-218</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento de pedidos: no se accede a uno ajeno</t>
+        </is>
+      </c>
+      <c r="D231" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre pedidos de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="74.38" customHeight="1">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t>CP-219</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento de pedidos: no se avanza el estado de uno ajeno</t>
+        </is>
+      </c>
+      <c r="D232" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre pedidos de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="74.38" customHeight="1">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>CP-220</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento de pedidos: no se usa un cliente de otra organización</t>
+        </is>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t>Dos organizaciones (A y B) con datos propios</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>Petición sobre pedidos de la organización B usando el token de A</t>
+        </is>
+      </c>
+      <c r="F233" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="74.38" customHeight="1">
+      <c r="A234" s="5" t="inlineStr">
+        <is>
+          <t>CP-221</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
           <t>Aislamiento de movimientos de stock: no se listan los de otra organización</t>
         </is>
       </c>
-      <c r="D223" s="6" t="inlineStr">
+      <c r="D234" s="6" t="inlineStr">
         <is>
           <t>Dos organizaciones (A y B) con datos propios</t>
         </is>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="E234" s="6" t="inlineStr">
         <is>
           <t>Petición sobre movimientos de stock de la organización B usando el token de A</t>
         </is>
       </c>
-      <c r="F223" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
         </is>
       </c>
-      <c r="G223" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="74.38" customHeight="1">
-      <c r="A224" s="5" t="inlineStr">
-        <is>
-          <t>CP-211</t>
-        </is>
-      </c>
-      <c r="B224" s="6" t="inlineStr">
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="74.38" customHeight="1">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t>CP-222</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
         <is>
           <t>Aislamiento multi-tenant</t>
         </is>
       </c>
-      <c r="C224" s="6" t="inlineStr">
+      <c r="C235" s="6" t="inlineStr">
         <is>
           <t>Aislamiento de movimientos de stock: no se accede a uno ajeno</t>
         </is>
       </c>
-      <c r="D224" s="6" t="inlineStr">
+      <c r="D235" s="6" t="inlineStr">
         <is>
           <t>Dos organizaciones (A y B) con datos propios</t>
         </is>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="E235" s="6" t="inlineStr">
         <is>
           <t>Petición sobre movimientos de stock de la organización B usando el token de A</t>
         </is>
       </c>
-      <c r="F224" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <t>HTTP 404 o lista sin el recurso ajeno: se responde como si no existiera, sin revelar su existencia.</t>
         </is>
       </c>
-      <c r="G224" s="7" t="inlineStr">
-        <is>
-          <t>Pasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="20" customHeight="1">
-      <c r="A225" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  RESUMEN: 211 casos de prueba documentados  |  10 módulos  |  Suite automatizada: 212 tests de backend, 0 fallos</t>
+      <c r="G235" s="7" t="inlineStr">
+        <is>
+          <t>Pasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="20" customHeight="1">
+      <c r="A236" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RESUMEN: 222 casos de prueba documentados  |  10 módulos  |  Suite automatizada: 0 fallos</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A185:G185"/>
-    <mergeCell ref="A204:G204"/>
-    <mergeCell ref="A225:G225"/>
+    <mergeCell ref="A236:G236"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A97:G97"/>
+    <mergeCell ref="A215:G215"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A153:G153"/>
+    <mergeCell ref="A171:G171"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A142:G142"/>
-    <mergeCell ref="A108:G108"/>
-    <mergeCell ref="A160:G160"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A196:G196"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A113:G113"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
